--- a/StatsJoueurs2526.xlsx
+++ b/StatsJoueurs2526.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mon Drive\Beaune Handball\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E270CD0-B510-4E6A-8C36-2AE298360C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3182DD37-B37B-433D-8656-B566FB5900F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{92067B7C-C8B8-49CF-AE5C-71A030AE0FF4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="2" activeTab="2" xr2:uid="{92067B7C-C8B8-49CF-AE5C-71A030AE0FF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil6" sheetId="6" r:id="rId1"/>
@@ -20,15 +20,17 @@
     <sheet name="StatJoueurs" sheetId="8" r:id="rId5"/>
     <sheet name="Discipline" sheetId="3" r:id="rId6"/>
     <sheet name="RefMatchs" sheetId="2" r:id="rId7"/>
+    <sheet name="RefJoueurs" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Arrêts!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">RefJoueurs!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">StatJoueurs!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId8"/>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="143">
   <si>
     <t>Match</t>
   </si>
@@ -388,6 +390,96 @@
   <si>
     <t>Tirs</t>
   </si>
+  <si>
+    <t>ARRIERE</t>
+  </si>
+  <si>
+    <t>Axel</t>
+  </si>
+  <si>
+    <t>GARDIEN</t>
+  </si>
+  <si>
+    <t>Corentin</t>
+  </si>
+  <si>
+    <t>AILIER</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>Kylian</t>
+  </si>
+  <si>
+    <t>PHAROSE</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Théo</t>
+  </si>
+  <si>
+    <t>DEMI-CENTRE</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>PIVOT</t>
+  </si>
+  <si>
+    <t>Gabin</t>
+  </si>
+  <si>
+    <t>Lilian</t>
+  </si>
+  <si>
+    <t>François</t>
+  </si>
+  <si>
+    <t>Mathieu</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
+  <si>
+    <t>Sasha</t>
+  </si>
+  <si>
+    <t>Léan</t>
+  </si>
+  <si>
+    <t>FAVERIN</t>
+  </si>
+  <si>
+    <t>Lubin</t>
+  </si>
+  <si>
+    <t>Marius</t>
+  </si>
+  <si>
+    <t>CHAZALON</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>BON</t>
+  </si>
+  <si>
+    <t>Poste</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
 </sst>
 </file>
 
@@ -396,7 +488,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +540,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -528,7 +627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -563,6 +662,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4189,7 +4289,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B5A8DBAF-01F0-4AEF-9A52-CD2C691FFA94}" name="Tableau croisé dynamique15" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B5A8DBAF-01F0-4AEF-9A52-CD2C691FFA94}" name="Tableau croisé dynamique15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4365,7 +4465,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68C3979C-CBB2-4B28-9378-7A0147F06D9F}" name="Tableau croisé dynamique16" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68C3979C-CBB2-4B28-9378-7A0147F06D9F}" name="Tableau croisé dynamique16" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D23" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0"/>
@@ -8942,7 +9042,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D84C6A3-D6F8-40C7-876A-7D69D758651E}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -9520,50 +9620,6 @@
       </c>
       <c r="D41">
         <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" t="s">
-        <v>110</v>
-      </c>
-      <c r="C45" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -13865,4 +13921,359 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F8D14E-B647-421B-B8A2-5507945DFEB6}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="15.06640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="16">
+        <v>21</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="16">
+        <v>15</v>
+      </c>
+      <c r="B4" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A11,""[A-Z]{2,}"")"),"COSNIER")</f>
+        <v>COSNIER</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="16">
+        <v>25</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="16">
+        <v>19</v>
+      </c>
+      <c r="B6" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A12,""[A-Z]{2,}"")"),"GOSTOMSKI")</f>
+        <v>GOSTOMSKI</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="16">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A9,""[A-Z]{2,}"")"),"GREGULSKI")</f>
+        <v>GREGULSKI</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A16,""[A-Z]{2,}"")"),"HERMAND")</f>
+        <v>HERMAND</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="16">
+        <v>16</v>
+      </c>
+      <c r="B9" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A21,""[A-Z]{2,}"")"),"MAI")</f>
+        <v>MAI</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A8,""[A-Z]{2,}"")"),"MINANA")</f>
+        <v>MINANA</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="16">
+        <v>24</v>
+      </c>
+      <c r="B11" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A15,""[A-Z]{2,}"")"),"MINY")</f>
+        <v>MINY</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="16">
+        <v>2</v>
+      </c>
+      <c r="B12" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A14,""[A-Z]{2,}"")"),"NAUDIN")</f>
+        <v>NAUDIN</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="16">
+        <v>3</v>
+      </c>
+      <c r="B13" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A2,""[A-Z]{2,}"")"),"NAUDIN")</f>
+        <v>NAUDIN</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="16">
+        <v>33</v>
+      </c>
+      <c r="B14" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A17,""[A-Z]{2,}"")"),"NAUDIN")</f>
+        <v>NAUDIN</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="16">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A7,""[A-Z]{2,}"")"),"PANIC")</f>
+        <v>PANIC</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="16">
+        <v>92</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="16">
+        <v>7</v>
+      </c>
+      <c r="B17" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A18,""[A-Z]{2,}"")"),"PLISSONNIER")</f>
+        <v>PLISSONNIER</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="16">
+        <v>12</v>
+      </c>
+      <c r="B18" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A20,""[A-Z]{2,}"")"),"STEPHAN")</f>
+        <v>STEPHAN</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="16">
+        <v>13</v>
+      </c>
+      <c r="B19" s="16" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(A10,""[A-Z]{2,}"")"),"THELCIDE")</f>
+        <v>THELCIDE</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{FA66C61F-1FED-49D2-8623-C0C94F830A4E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>